--- a/src/src1/assets/Customer_Format.xlsx
+++ b/src/src1/assets/Customer_Format.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zulaa/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666F62C9-5E15-2742-829F-942BCDB29E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6911976-6C9E-CF47-836F-EBF1D466FDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10080" yWindow="4740" windowWidth="18160" windowHeight="12920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>test aba</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>Авлага</t>
+  </si>
+  <si>
+    <t>Авлагын лимит</t>
   </si>
 </sst>
 </file>
@@ -126,13 +129,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -414,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.83203125" style="1" customWidth="1"/>
@@ -422,11 +428,12 @@
     <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="13.33203125" customWidth="1"/>
-    <col min="6" max="6" width="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -445,11 +452,14 @@
       <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -469,6 +479,9 @@
         <v>10</v>
       </c>
       <c r="G2" s="3">
+        <v>100000</v>
+      </c>
+      <c r="H2" s="3">
         <v>100000</v>
       </c>
     </row>
